--- a/data/trans_orig/Predimed-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Predimed-Edad-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de adherencia a la dieta mediterránea (Predimed)</t>
+          <t>Puntuación media de la escala de adherencia a la dieta mediterránea (Predimed) (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 6,42</t>
+          <t>5,66; 6,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 6,14</t>
+          <t>5,49; 6,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 6,19</t>
+          <t>5,7; 6,2</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 6,39</t>
+          <t>5,79; 6,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 6,48</t>
+          <t>6,01; 6,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 6,35</t>
+          <t>5,99; 6,36</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 6,57</t>
+          <t>6,13; 6,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 6,47</t>
+          <t>6,12; 6,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 6,46</t>
+          <t>6,16; 6,44</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 6,87</t>
+          <t>6,42; 6,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,44</t>
+          <t>6,66; 7,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 6,97</t>
+          <t>6,58; 6,97</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,35; 6,72</t>
+          <t>6,33; 6,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,49; 6,91</t>
+          <t>6,48; 6,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,74; 7,69</t>
+          <t>6,74; 7,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 7,46</t>
+          <t>6,71; 7,5</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,19; 6,53</t>
+          <t>6,18; 6,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,26; 6,54</t>
+          <t>6,25; 6,54</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,45; 6,85</t>
+          <t>6,44; 6,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,42; 6,67</t>
+          <t>6,42; 6,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Predimed-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Predimed-Edad-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,05</t>
+          <t>5,91</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,81</t>
+          <t>5,82</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>5,87</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 6,41</t>
+          <t>5,57; 6,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 6,19</t>
+          <t>5,5; 6,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 6,2</t>
+          <t>5,65; 6,13</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,07</t>
+          <t>6,06</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,24</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,17</t>
+          <t>6,14</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 6,4</t>
+          <t>5,75; 6,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 6,43</t>
+          <t>5,98; 6,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 6,36</t>
+          <t>5,96; 6,31</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,33</t>
+          <t>6,29</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>6,28</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>6,29</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,31</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 6,56</t>
+          <t>6,08; 6,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 6,45</t>
+          <t>6,13; 6,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 6,44</t>
+          <t>6,15; 6,41</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>6,53</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>6,64</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,76</t>
+          <t>6,59</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 6,89</t>
+          <t>6,35; 6,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 7,45</t>
+          <t>6,49; 6,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,58; 6,97</t>
+          <t>6,47; 6,7</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,52</t>
+          <t>6,51</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,64</t>
+          <t>6,61</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>6,56</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 6,72</t>
+          <t>6,33; 6,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 6,79</t>
+          <t>6,45; 6,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 6,7</t>
+          <t>6,46; 6,7</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7,21</t>
+          <t>6,77</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>6,75</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,48; 6,93</t>
+          <t>6,53; 6,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,74; 7,73</t>
+          <t>6,59; 6,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,71; 7,5</t>
+          <t>6,6; 6,89</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,47</t>
+          <t>6,46</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>6,35</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,4</t>
+          <t>6,39</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 6,75</t>
+          <t>6,19; 6,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,18; 6,52</t>
+          <t>6,17; 6,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,25; 6,54</t>
+          <t>6,25; 6,53</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6,44</t>
+          <t>6,37</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>6,4</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,34; 6,57</t>
+          <t>6,28; 6,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,44; 6,88</t>
+          <t>6,35; 6,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,42; 6,68</t>
+          <t>6,33; 6,45</t>
         </is>
       </c>
     </row>
